--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486948_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486948_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1837</v>
+        <v>2.9968</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2752</v>
+        <v>1.2364</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9086</v>
+        <v>1.7604</v>
       </c>
       <c r="G2" t="n">
         <v>1.2105</v>
@@ -610,13 +610,13 @@
         <v>2.8748</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0911</v>
+        <v>-0.0959</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.283</v>
+        <v>-0.3217</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3741</v>
+        <v>0.2259</v>
       </c>
       <c r="V2" t="n">
         <v>1.0608</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. BITJAA KODY</t>
+          <t>D. ILINCIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6312</v>
+        <v>1.9734</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6373</v>
+        <v>0.511</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0061</v>
+        <v>1.4623</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6832</v>
+        <v>0.6018</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.1483</v>
+        <v>0.2597</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8315</v>
+        <v>0.3422</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8742</v>
+        <v>0.8249</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6516</v>
+        <v>0.7855</v>
       </c>
       <c r="L3" t="n">
-        <v>2.5258</v>
+        <v>0.0395</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.191</v>
+        <v>-0.2231</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4967</v>
+        <v>-0.5258</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6943</v>
+        <v>0.3027</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0267</v>
+        <v>1.6427</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0534</v>
+        <v>1.6427</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7372</v>
+        <v>-0.2712</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3093</v>
+        <v>-0.3139</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4279</v>
+        <v>0.0427</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.8159999999999999</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4805</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2965</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. ILINCIC</t>
+          <t>G. PEREZ RAMIREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0888</v>
+        <v>1.6683</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8636</v>
+        <v>-0.3394</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2252</v>
+        <v>2.0077</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6018</v>
+        <v>-0.2653</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2597</v>
+        <v>1.3397</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3422</v>
+        <v>-1.6051</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8249</v>
+        <v>-0.2269</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7855</v>
+        <v>1.8916</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0395</v>
+        <v>-2.1185</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2231</v>
+        <v>-0.0385</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5258</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3027</v>
+        <v>0.5134</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6427</v>
+        <v>2.6694</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6427</v>
+        <v>2.6694</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1558</v>
+        <v>-0.8582</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0386</v>
+        <v>-0.3527</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1944</v>
+        <v>-0.5054</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.1224</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1179</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. PEREZ RAMIREZ</t>
+          <t>J. SOLER CIRUJEDA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7524</v>
+        <v>1.3262</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1961</v>
+        <v>0.9456</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9484</v>
+        <v>0.3806</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2653</v>
+        <v>2.798</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3397</v>
+        <v>2.0666</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.6051</v>
+        <v>0.7315</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2269</v>
+        <v>3.5683</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8916</v>
+        <v>2.3977</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.1185</v>
+        <v>1.1706</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0385</v>
+        <v>-0.7702</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.3311</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5134</v>
+        <v>-0.4391</v>
       </c>
       <c r="P5" t="n">
-        <v>2.6694</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="R5" t="n">
-        <v>2.6694</v>
+        <v>1.4374</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7741</v>
+        <v>-0.4184</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2094</v>
+        <v>-0.3721</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5647</v>
+        <v>-0.0464</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1224</v>
+        <v>0.5893</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2402</v>
+        <v>0.8295</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1179</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SOLER CIRUJEDA</t>
+          <t>J. BITJAA KODY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0264</v>
+        <v>1.3027</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5272</v>
+        <v>1.4867</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4991</v>
+        <v>-0.184</v>
       </c>
       <c r="G6" t="n">
-        <v>2.798</v>
+        <v>0.6832</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0666</v>
+        <v>-1.1483</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7315</v>
+        <v>1.8315</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5683</v>
+        <v>1.8742</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3977</v>
+        <v>-0.6516</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1706</v>
+        <v>2.5258</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7702</v>
+        <v>-1.191</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3311</v>
+        <v>-0.4967</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4391</v>
+        <v>-0.6943</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.6427</v>
+        <v>1.0267</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.0801</v>
+        <v>-1.0267</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4374</v>
+        <v>2.0534</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7183</v>
+        <v>0.4088</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7905</v>
+        <v>0.1587</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0722</v>
+        <v>0.2501</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5893</v>
+        <v>-0.8159999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8295</v>
+        <v>0.4805</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2402</v>
+        <v>-1.2965</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0629</v>
+        <v>-0.6362</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8083</v>
+        <v>-1.1148</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7454</v>
+        <v>0.4786</v>
       </c>
       <c r="G7" t="n">
         <v>1.1402</v>
@@ -1000,13 +1000,13 @@
         <v>3.0801</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1037</v>
+        <v>-0.677</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2438</v>
+        <v>-0.5504</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1401</v>
+        <v>-0.1267</v>
       </c>
       <c r="V7" t="n">
         <v>-2.126</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1339</v>
+        <v>-0.7468</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9481000000000001</v>
+        <v>-0.7389</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1858</v>
+        <v>-0.008</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8495</v>
@@ -1078,13 +1078,13 @@
         <v>0.8214</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1058</v>
+        <v>-0.7187</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3875</v>
+        <v>-0.1783</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7183</v>
+        <v>-0.5404</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2976</v>
+        <v>-3.3115</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6369</v>
+        <v>-0.5323</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.6606</v>
+        <v>-2.7792</v>
       </c>
       <c r="G9" t="n">
         <v>-2.501</v>
@@ -1156,13 +1156,13 @@
         <v>1.0267</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6447000000000001</v>
+        <v>-0.6586</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3139</v>
+        <v>-0.2093</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3307</v>
+        <v>-0.4493</v>
       </c>
       <c r="V9" t="n">
         <v>-1.1786</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.4005</v>
+        <v>-4.5448</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.9871</v>
+        <v>-3.3982</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4134</v>
+        <v>-1.1466</v>
       </c>
       <c r="G10" t="n">
         <v>-2.5004</v>
@@ -1234,13 +1234,13 @@
         <v>2.8748</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.31</v>
+        <v>-0.4543</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9726</v>
+        <v>-0.3837</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3373</v>
+        <v>-0.0706</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3581</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.5366</v>
+        <v>-6.4476</v>
       </c>
       <c r="E11" t="n">
         <v>-5.8755</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.661</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>-2.5282</v>
@@ -1312,13 +1312,13 @@
         <v>1.0267</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4909</v>
+        <v>-0.4019</v>
       </c>
       <c r="T11" t="n">
         <v>-0.4611</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0298</v>
+        <v>0.0592</v>
       </c>
       <c r="V11" t="n">
         <v>0.5893</v>
@@ -1345,25 +1345,25 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.749000000000001</v>
+        <v>-6.4195</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.1487</v>
+        <v>-7.8194</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3998</v>
+        <v>1.399699999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.2107</v>
+        <v>-2.210699999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6824</v>
+        <v>0.6823999999999991</v>
       </c>
       <c r="I12" t="n">
         <v>-2.8928</v>
       </c>
       <c r="J12" t="n">
-        <v>7.292900000000001</v>
+        <v>7.292899999999999</v>
       </c>
       <c r="K12" t="n">
         <v>5.0974</v>
@@ -1381,7 +1381,7 @@
         <v>-5.0886</v>
       </c>
       <c r="P12" t="n">
-        <v>2.0534</v>
+        <v>2.053400000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>-17.454</v>
@@ -1390,16 +1390,16 @@
         <v>19.5074</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.475</v>
+        <v>-4.1454</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.3139</v>
+        <v>-2.9845</v>
       </c>
       <c r="U12" t="n">
         <v>-1.1609</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.1169</v>
+        <v>-2.116899999999999</v>
       </c>
       <c r="W12" t="n">
         <v>5.3263</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.6952</v>
+        <v>3.9672</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7767</v>
+        <v>1.6721</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9185</v>
+        <v>2.2951</v>
       </c>
       <c r="G13" t="n">
         <v>1.2195</v>
@@ -1468,13 +1468,13 @@
         <v>2.8748</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1054</v>
+        <v>0.1666</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2907</v>
+        <v>-0.3953</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1853</v>
+        <v>0.5619</v>
       </c>
       <c r="V13" t="n">
         <v>0.9384</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. FANER CATALA</t>
+          <t>P. GARCIA CARRERO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1542</v>
+        <v>3.4482</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7063</v>
+        <v>1.6808</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5521</v>
+        <v>1.7674</v>
       </c>
       <c r="G14" t="n">
-        <v>3.133</v>
+        <v>1.3813</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7072000000000001</v>
+        <v>1.8523</v>
       </c>
       <c r="I14" t="n">
-        <v>2.4258</v>
+        <v>-0.4709</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8374</v>
+        <v>1.5593</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7855</v>
+        <v>1.4278</v>
       </c>
       <c r="L14" t="n">
-        <v>3.0519</v>
+        <v>0.1314</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7044</v>
+        <v>-0.1779</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.07829999999999999</v>
+        <v>0.4244</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6261</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.0267</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.2588</v>
+        <v>-2.4641</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2321</v>
+        <v>2.2588</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2882</v>
+        <v>1.3338</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.2284</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3391</v>
+        <v>1.1054</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2402</v>
+        <v>0.9384</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1786</v>
+        <v>2.3573</v>
       </c>
       <c r="X14" t="n">
         <v>-1.4189</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. GARCIA CARRERO</t>
+          <t>K. NEWTON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0595</v>
+        <v>2.815</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9486</v>
+        <v>2.7585</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1109</v>
+        <v>0.0566</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3813</v>
+        <v>1.0261</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8523</v>
+        <v>-0.289</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4709</v>
+        <v>1.315</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5593</v>
+        <v>2.0883</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4278</v>
+        <v>0.6813</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1314</v>
+        <v>1.407</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1779</v>
+        <v>-1.0623</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4244</v>
+        <v>-0.9703000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.092</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2053</v>
+        <v>0.4107</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.4641</v>
+        <v>-0.4107</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2588</v>
+        <v>0.8214</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.8978</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5038</v>
+        <v>0.6004</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4489</v>
+        <v>0.2974</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9384</v>
+        <v>0.4805</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3573</v>
+        <v>0.4805</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. NEWTON</t>
+          <t>J. FANER CATALA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3181</v>
+        <v>2.8143</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5493</v>
+        <v>3.0787</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2311</v>
+        <v>-0.2644</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0261</v>
+        <v>3.133</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.289</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>1.315</v>
+        <v>2.4258</v>
       </c>
       <c r="J16" t="n">
-        <v>2.0883</v>
+        <v>3.8374</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6813</v>
+        <v>0.7855</v>
       </c>
       <c r="L16" t="n">
-        <v>1.407</v>
+        <v>3.0519</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0623</v>
+        <v>-0.7044</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9703000000000001</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.092</v>
+        <v>-0.6261</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4107</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.4107</v>
+        <v>-2.2588</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8214</v>
+        <v>1.2321</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4009</v>
+        <v>0.9482</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3912</v>
+        <v>0.3214</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0098</v>
+        <v>0.6268</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4805</v>
+        <v>-0.2402</v>
       </c>
       <c r="W16" t="n">
-        <v>0.4805</v>
+        <v>1.1786</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.951</v>
+        <v>1.9441</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6803</v>
+        <v>-1.2033</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6313</v>
+        <v>3.1474</v>
       </c>
       <c r="G17" t="n">
         <v>0.2889</v>
@@ -1780,13 +1780,13 @@
         <v>2.4641</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7237</v>
+        <v>0.7168</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8173</v>
+        <v>0.2943</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0936</v>
+        <v>0.4225</v>
       </c>
       <c r="V17" t="n">
         <v>0.9384</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5258</v>
+        <v>0.6283</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.216</v>
+        <v>-0.3791</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6901</v>
+        <v>1.0075</v>
       </c>
       <c r="G18" t="n">
         <v>0.5645</v>
@@ -1858,13 +1858,13 @@
         <v>2.0534</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6796</v>
+        <v>0.4745</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9649</v>
+        <v>-0.1281</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2853</v>
+        <v>0.6026</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K.  BAOKO</t>
+          <t>R. FABREGA URPINA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8273</v>
+        <v>-1.9216</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1244</v>
+        <v>-3.9134</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7029</v>
+        <v>1.9919</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7373</v>
+        <v>-0.1616</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7006</v>
+        <v>-1.1061</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0368</v>
+        <v>0.9445</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0116</v>
+        <v>0.4531</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0905</v>
+        <v>-0.1649</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0789</v>
+        <v>0.6181</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7258</v>
+        <v>-0.6147</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6101</v>
+        <v>-0.9412</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1157</v>
+        <v>0.3264</v>
       </c>
       <c r="P19" t="n">
-        <v>0.616</v>
+        <v>-2.2588</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2053</v>
+        <v>-4.5175</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8214</v>
+        <v>2.2588</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6512</v>
+        <v>0.2586</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4416</v>
+        <v>-0.0892</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2097</v>
+        <v>0.3479</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.3573</v>
+        <v>0.2402</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3491</v>
+        <v>0.2402</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.0082</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. ANDREATTA</t>
+          <t>K.  BAOKO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4762</v>
+        <v>-2.0069</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.8188</v>
+        <v>-0.3336</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3426</v>
+        <v>-1.6733</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.5037</v>
+        <v>-0.7373</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.7511</v>
+        <v>-0.7006</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7526</v>
+        <v>-0.0368</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.5447</v>
+        <v>-0.0116</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.255</v>
+        <v>-0.0905</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2897</v>
+        <v>0.0789</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9589</v>
+        <v>-0.7258</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4961</v>
+        <v>-0.6101</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4629</v>
+        <v>-0.1157</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.8214</v>
+        <v>0.616</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.4908</v>
+        <v>-0.2053</v>
       </c>
       <c r="R20" t="n">
-        <v>2.6694</v>
+        <v>0.8214</v>
       </c>
       <c r="S20" t="n">
-        <v>1.6702</v>
+        <v>0.4717</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0381</v>
+        <v>0.2324</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6321</v>
+        <v>0.2393</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1786</v>
+        <v>-2.3573</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1786</v>
+        <v>-0.3491</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.0082</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. FABREGA URPINA</t>
+          <t>M. ANDREATTA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5997</v>
+        <v>-3.5449</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.541</v>
+        <v>-4.7602</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9413</v>
+        <v>1.2153</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1616</v>
+        <v>-4.5037</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1061</v>
+        <v>-2.7511</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9445</v>
+        <v>-1.7526</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4531</v>
+        <v>-2.5447</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1649</v>
+        <v>-1.255</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6181</v>
+        <v>-1.2897</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6147</v>
+        <v>-1.9589</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9412</v>
+        <v>-1.4961</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3264</v>
+        <v>-0.4629</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.2588</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.5175</v>
+        <v>-3.4908</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2588</v>
+        <v>2.6694</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4196</v>
+        <v>0.6015</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7169</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2973</v>
+        <v>0.5048</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2402</v>
+        <v>1.1786</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2402</v>
+        <v>1.1786</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>6.748999999999999</v>
+        <v>8.143699999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3996</v>
+        <v>-1.399499999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>8.1486</v>
+        <v>9.543500000000002</v>
       </c>
       <c r="G22" t="n">
-        <v>2.210699999999999</v>
+        <v>2.2107</v>
       </c>
       <c r="H22" t="n">
         <v>-0.6823000000000001</v>
@@ -2143,7 +2143,7 @@
         <v>2.8928</v>
       </c>
       <c r="J22" t="n">
-        <v>9.503499999999997</v>
+        <v>9.503500000000001</v>
       </c>
       <c r="K22" t="n">
         <v>4.4151</v>
@@ -2155,7 +2155,7 @@
         <v>-7.293</v>
       </c>
       <c r="N22" t="n">
-        <v>-5.0975</v>
+        <v>-5.097499999999999</v>
       </c>
       <c r="O22" t="n">
         <v>-2.1957</v>
@@ -2170,16 +2170,16 @@
         <v>17.4542</v>
       </c>
       <c r="S22" t="n">
-        <v>4.4747</v>
+        <v>5.869499999999999</v>
       </c>
       <c r="T22" t="n">
         <v>1.161</v>
       </c>
       <c r="U22" t="n">
-        <v>3.3139</v>
+        <v>4.708600000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>2.117</v>
+        <v>2.117000000000001</v>
       </c>
       <c r="W22" t="n">
         <v>7.443300000000001</v>
